--- a/Result/profitability/6167.xlsx
+++ b/Result/profitability/6167.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06999999999999999</v>
+        <v>-0.08124999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>7.03375</v>
+        <v>6.56</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1925</v>
+        <v>-0.21875</v>
       </c>
       <c r="N3" t="n">
-        <v>5.28</v>
+        <v>4.90875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.32875</v>
+        <v>-0.3375</v>
       </c>
       <c r="N4" t="n">
-        <v>3.59875</v>
+        <v>3.17875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.45625</v>
+        <v>-0.465</v>
       </c>
       <c r="N5" t="n">
-        <v>2.19</v>
+        <v>1.72375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6525000000000001</v>
+        <v>-0.6737500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.427500000000001</v>
+        <v>-4.040000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7575000000000001</v>
+        <v>-0.765</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.8725</v>
+        <v>-5.383750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8237500000000001</v>
+        <v>-0.8287500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.635000000000001</v>
+        <v>-6.025000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.82625</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.61125</v>
+        <v>-3.611250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.6587499999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3100000000000005</v>
+        <v>-0.3100000000000009</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>297</v>
+      </c>
+      <c r="D75" t="n">
+        <v>286</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-14.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.01125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.865</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4629080118694362</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5074829931972789</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
